--- a/output/hrv/female_HFD_HRV_AIC_ECG_calculated_num_k_is_50_kmax_is_20_window_step_is_None.xlsx
+++ b/output/hrv/female_HFD_HRV_AIC_ECG_calculated_num_k_is_50_kmax_is_20_window_step_is_None.xlsx
@@ -5,17 +5,30 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\ECGBiologicalAge\HeartAge\output\hrv\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Projects\HeartAge\output\hrv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7BD38D22-3446-4C9D-949D-6A5B47A0CD03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D40C4E6-AC39-4BDD-8213-735F5BB5F556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{1F684655-F0C3-4304-BF00-1C3D071B1060}"/>
   </bookViews>
   <sheets>
     <sheet name="female_HFD_HRV_AIC_ECG_calculat" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -579,48 +592,48 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% – колірна тема 1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% – колірна тема 2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% – колірна тема 3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% – колірна тема 4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% – колірна тема 5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% – колірна тема 6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% – колірна тема 1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% – колірна тема 2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% – колірна тема 3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% – колірна тема 4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% – колірна тема 5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% – колірна тема 6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% – колірна тема 1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% – колірна тема 2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% – колірна тема 3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% – колірна тема 4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% – колірна тема 5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% – колірна тема 6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Ввід" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Гарний" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Заголовок 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Заголовок 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Заголовок 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Заголовок 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
-    <cellStyle name="Зв'язана клітинка" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Колірна тема 1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Колірна тема 2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Колірна тема 3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Колірна тема 4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Колірна тема 5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Колірна тема 6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Контрольна клітинка" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Назва" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Нейтральний" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Обчислення" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Підсумок" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Поганий" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Примітка" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Результат" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Текст попередження" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="Текст пояснення" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -638,7 +651,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="uk-UA"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2019,16 +2032,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>438149</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>14287</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>561974</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>119062</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>485774</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>609599</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>90487</xdr:rowOff>
+      <xdr:rowOff>4762</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2057,9 +2070,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Офіс">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2097,7 +2110,7 @@
         <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Офіс">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
@@ -2203,7 +2216,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Офіс">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2373,10 +2386,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98259CCF-FC1E-47DA-90DF-9D63BE4E9313}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>15</v>
       </c>
@@ -2387,7 +2400,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2400,8 +2413,12 @@
       <c r="D2">
         <v>1.9570000000000001</v>
       </c>
+      <c r="E2">
+        <f>AVERAGE(LEFT(A2,FIND(" -",A2)-1),MID(A2,FIND("-",A2)+2,LEN(A2)))</f>
+        <v>18.5</v>
+      </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -2414,8 +2431,12 @@
       <c r="D3">
         <v>1.956</v>
       </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E16" si="0">AVERAGE(LEFT(A3,FIND(" -",A3)-1),MID(A3,FIND("-",A3)+2,LEN(A3)))</f>
+        <v>22</v>
+      </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -2428,8 +2449,12 @@
       <c r="D4">
         <v>1.9550000000000001</v>
       </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -2442,8 +2467,12 @@
       <c r="D5">
         <v>1.96</v>
       </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -2456,8 +2485,12 @@
       <c r="D6">
         <v>1.9650000000000001</v>
       </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -2470,8 +2503,12 @@
       <c r="D7">
         <v>1.94</v>
       </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -2484,8 +2521,12 @@
       <c r="D8">
         <v>1.9179999999999999</v>
       </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -2498,8 +2539,12 @@
       <c r="D9">
         <v>1.9259999999999999</v>
       </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -2512,8 +2557,12 @@
       <c r="D10">
         <v>1.92</v>
       </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -2526,8 +2575,12 @@
       <c r="D11">
         <v>1.9330000000000001</v>
       </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -2540,8 +2593,12 @@
       <c r="D12">
         <v>1.944</v>
       </c>
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>67</v>
+      </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -2554,8 +2611,12 @@
       <c r="D13">
         <v>1.9019999999999999</v>
       </c>
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -2568,8 +2629,12 @@
       <c r="D14">
         <v>1.9359999999999999</v>
       </c>
+      <c r="E14">
+        <f t="shared" si="0"/>
+        <v>77</v>
+      </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -2582,8 +2647,12 @@
       <c r="D15">
         <v>1.958</v>
       </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>82</v>
+      </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -2595,6 +2664,16 @@
       </c>
       <c r="D16">
         <v>1.9379999999999999</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="0"/>
+        <v>88.5</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <f>CORREL(E2:E16,B2:B16)</f>
+        <v>-0.45099742166124357</v>
       </c>
     </row>
   </sheetData>

--- a/output/hrv/female_HFD_HRV_AIC_ECG_calculated_num_k_is_50_kmax_is_20_window_step_is_None.xlsx
+++ b/output/hrv/female_HFD_HRV_AIC_ECG_calculated_num_k_is_50_kmax_is_20_window_step_is_None.xlsx
@@ -5,43 +5,27 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Projects\HeartAge\output\hrv\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\ECGBiologicalAge\HeartAge\output\hrv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D40C4E6-AC39-4BDD-8213-735F5BB5F556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{29734E18-E272-46BF-BD9D-8BD8F7C00258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{1F684655-F0C3-4304-BF00-1C3D071B1060}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{86F6570E-A946-4364-9389-C91694397059}"/>
   </bookViews>
   <sheets>
     <sheet name="female_HFD_HRV_AIC_ECG_calculat" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>20 - 24</t>
   </si>
   <si>
     <t>25 - 29</t>
-  </si>
-  <si>
-    <t>30 - 34</t>
   </si>
   <si>
     <t>18 - 19</t>
@@ -56,10 +40,10 @@
     <t>40 - 44</t>
   </si>
   <si>
-    <t>55 - 59</t>
+    <t>30 - 34</t>
   </si>
   <si>
-    <t>75 - 79</t>
+    <t>60 - 64</t>
   </si>
   <si>
     <t>35 - 39</t>
@@ -68,7 +52,10 @@
     <t>65 - 69</t>
   </si>
   <si>
-    <t>60 - 64</t>
+    <t>80 - 84</t>
+  </si>
+  <si>
+    <t>55 - 59</t>
   </si>
   <si>
     <t>85 - 92</t>
@@ -77,16 +64,7 @@
     <t>70 - 74</t>
   </si>
   <si>
-    <t>80 - 84</t>
-  </si>
-  <si>
-    <t>k_max=7</t>
-  </si>
-  <si>
-    <t>k_max=20</t>
-  </si>
-  <si>
-    <t>k_max=44</t>
+    <t>75 - 79</t>
   </si>
 </sst>
 </file>
@@ -592,48 +570,48 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="20% – колірна тема 1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% – колірна тема 2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% – колірна тема 3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% – колірна тема 4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% – колірна тема 5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% – колірна тема 6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% – колірна тема 1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% – колірна тема 2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% – колірна тема 3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% – колірна тема 4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% – колірна тема 5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% – колірна тема 6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% – колірна тема 1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% – колірна тема 2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% – колірна тема 3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% – колірна тема 4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% – колірна тема 5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% – колірна тема 6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Ввід" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Гарний" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Заголовок 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Заголовок 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Заголовок 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Заголовок 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
+    <cellStyle name="Зв'язана клітинка" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Колірна тема 1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Колірна тема 2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Колірна тема 3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Колірна тема 4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Колірна тема 5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Колірна тема 6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Контрольна клітинка" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Назва" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Нейтральний" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Обчислення" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Підсумок" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Поганий" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Примітка" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Результат" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Текст попередження" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Текст пояснення" xfId="16" builtinId="53" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -651,7 +629,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="uk-UA"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -663,46 +641,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:sysClr>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>Higuchi fractal dimension (HFD) for fractal HRV time series per each age range for all females </a:t>
-            </a:r>
-            <a:endParaRPr lang="uk-UA" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:sysClr>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </c:rich>
-      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -741,17 +679,6 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>female_HFD_HRV_AIC_ECG_calculat!$B$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>k_max=7</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
@@ -766,7 +693,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>female_HFD_HRV_AIC_ECG_calculat!$A$2:$A$16</c:f>
+              <c:f>female_HFD_HRV_AIC_ECG_calculat!$A$1:$A$15</c:f>
               <c:strCache>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
@@ -819,54 +746,54 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>female_HFD_HRV_AIC_ECG_calculat!$B$2:$B$16</c:f>
+              <c:f>female_HFD_HRV_AIC_ECG_calculat!$B$1:$B$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.9570000000000001</c:v>
+                  <c:v>1.9750000000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.956</c:v>
+                  <c:v>1.964</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.9550000000000001</c:v>
+                  <c:v>1.9590000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.96</c:v>
+                  <c:v>1.964</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>1.9650000000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.94</c:v>
+                  <c:v>1.9390000000000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.9179999999999999</c:v>
+                  <c:v>1.925</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.9259999999999999</c:v>
+                  <c:v>1.9330000000000001</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.92</c:v>
+                  <c:v>1.9450000000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.9330000000000001</c:v>
+                  <c:v>1.9419999999999999</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.944</c:v>
+                  <c:v>1.895</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.9019999999999999</c:v>
+                  <c:v>1.972</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.9359999999999999</c:v>
+                  <c:v>1.788</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.958</c:v>
+                  <c:v>2.0019999999999998</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.9379999999999999</c:v>
+                  <c:v>1.978</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -874,287 +801,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-BA15-414E-9DD7-099ACF911730}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>female_HFD_HRV_AIC_ECG_calculat!$C$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>k_max=20</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>female_HFD_HRV_AIC_ECG_calculat!$A$2:$A$16</c:f>
-              <c:strCache>
-                <c:ptCount val="15"/>
-                <c:pt idx="0">
-                  <c:v>18 - 19</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>20 - 24</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>25 - 29</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>30 - 34</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>35 - 39</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>40 - 44</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>45 - 49</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>50 - 54</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>55 - 59</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>60 - 64</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>65 - 69</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>70 - 74</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>75 - 79</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>80 - 84</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>85 - 92</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>female_HFD_HRV_AIC_ECG_calculat!$C$2:$C$16</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
-                <c:pt idx="0">
-                  <c:v>1.9570000000000001</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.956</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.9550000000000001</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.96</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.9650000000000001</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1.94</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1.9179999999999999</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1.9259999999999999</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1.92</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1.9330000000000001</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1.944</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1.9019999999999999</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1.9359999999999999</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1.958</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1.9379999999999999</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-BA15-414E-9DD7-099ACF911730}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>female_HFD_HRV_AIC_ECG_calculat!$D$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>k_max=44</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>female_HFD_HRV_AIC_ECG_calculat!$A$2:$A$16</c:f>
-              <c:strCache>
-                <c:ptCount val="15"/>
-                <c:pt idx="0">
-                  <c:v>18 - 19</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>20 - 24</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>25 - 29</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>30 - 34</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>35 - 39</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>40 - 44</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>45 - 49</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>50 - 54</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>55 - 59</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>60 - 64</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>65 - 69</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>70 - 74</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>75 - 79</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>80 - 84</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>85 - 92</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>female_HFD_HRV_AIC_ECG_calculat!$D$2:$D$16</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
-                <c:pt idx="0">
-                  <c:v>1.9570000000000001</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.956</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.9550000000000001</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.96</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.9650000000000001</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1.94</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1.9179999999999999</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1.9259999999999999</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1.92</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1.9330000000000001</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1.944</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1.9019999999999999</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1.9359999999999999</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1.958</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1.9379999999999999</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-BA15-414E-9DD7-099ACF911730}"/>
+              <c16:uniqueId val="{00000000-9565-4E22-9E95-6BA7F9AB64F7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1167,72 +814,16 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1135985056"/>
-        <c:axId val="1135978816"/>
+        <c:axId val="1943348704"/>
+        <c:axId val="1943331424"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1135985056"/>
+        <c:axId val="1943348704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Age range</a:t>
-                </a:r>
-                <a:endParaRPr lang="uk-UA"/>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="uk-UA"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1270,7 +861,7 @@
             <a:endParaRPr lang="uk-UA"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1135978816"/>
+        <c:crossAx val="1943331424"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1278,7 +869,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1135978816"/>
+        <c:axId val="1943331424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1298,62 +889,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>HFD</a:t>
-                </a:r>
-                <a:endParaRPr lang="uk-UA"/>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="uk-UA"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1385,7 +920,7 @@
             <a:endParaRPr lang="uk-UA"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1135985056"/>
+        <c:crossAx val="1943348704"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1397,37 +932,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="uk-UA"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -2032,23 +1536,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>561974</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>119062</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>609599</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>14287</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>609599</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>428624</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>4762</xdr:rowOff>
+      <xdr:rowOff>90487</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Діаграма 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F396427-6BE4-D174-F88B-5CD459CD3A85}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D312D7FD-DB68-1094-CC62-CA63B808FC86}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2070,9 +1574,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Офіс">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2110,7 +1614,7 @@
         <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Офіс">
       <a:majorFont>
         <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
@@ -2216,7 +1720,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Офіс">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2385,300 +1889,133 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98259CCF-FC1E-47DA-90DF-9D63BE4E9313}">
-  <dimension ref="A1:E18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E67A2145-FC62-41A7-943C-EB329AF1B312}">
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" t="s">
-        <v>17</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1">
+        <v>1.9750000000000001</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>1.964</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>1.9590000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1.964</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>1.9650000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1.9390000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
-        <v>1.9570000000000001</v>
-      </c>
-      <c r="C2">
-        <v>1.9570000000000001</v>
-      </c>
-      <c r="D2">
-        <v>1.9570000000000001</v>
-      </c>
-      <c r="E2">
-        <f>AVERAGE(LEFT(A2,FIND(" -",A2)-1),MID(A2,FIND("-",A2)+2,LEN(A2)))</f>
-        <v>18.5</v>
+      <c r="B7">
+        <v>1.925</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3">
-        <v>1.956</v>
-      </c>
-      <c r="C3">
-        <v>1.956</v>
-      </c>
-      <c r="D3">
-        <v>1.956</v>
-      </c>
-      <c r="E3">
-        <f t="shared" ref="E3:E16" si="0">AVERAGE(LEFT(A3,FIND(" -",A3)-1),MID(A3,FIND("-",A3)+2,LEN(A3)))</f>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>1.9550000000000001</v>
-      </c>
-      <c r="C4">
-        <v>1.9550000000000001</v>
-      </c>
-      <c r="D4">
-        <v>1.9550000000000001</v>
-      </c>
-      <c r="E4">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>1.96</v>
-      </c>
-      <c r="C5">
-        <v>1.96</v>
-      </c>
-      <c r="D5">
-        <v>1.96</v>
-      </c>
-      <c r="E5">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>1.9650000000000001</v>
-      </c>
-      <c r="C6">
-        <v>1.9650000000000001</v>
-      </c>
-      <c r="D6">
-        <v>1.9650000000000001</v>
-      </c>
-      <c r="E6">
-        <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>1.94</v>
-      </c>
-      <c r="C7">
-        <v>1.94</v>
-      </c>
-      <c r="D7">
-        <v>1.94</v>
-      </c>
-      <c r="E7">
-        <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
       <c r="B8">
-        <v>1.9179999999999999</v>
-      </c>
-      <c r="C8">
-        <v>1.9179999999999999</v>
-      </c>
-      <c r="D8">
-        <v>1.9179999999999999</v>
-      </c>
-      <c r="E8">
-        <f t="shared" si="0"/>
-        <v>47</v>
+        <v>1.9330000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B9">
-        <v>1.9259999999999999</v>
-      </c>
-      <c r="C9">
-        <v>1.9259999999999999</v>
-      </c>
-      <c r="D9">
-        <v>1.9259999999999999</v>
-      </c>
-      <c r="E9">
-        <f t="shared" si="0"/>
-        <v>52</v>
+        <v>1.9450000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
       <c r="B10">
-        <v>1.92</v>
-      </c>
-      <c r="C10">
-        <v>1.92</v>
-      </c>
-      <c r="D10">
-        <v>1.92</v>
-      </c>
-      <c r="E10">
-        <f t="shared" si="0"/>
-        <v>57</v>
+        <v>1.9419999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B11">
-        <v>1.9330000000000001</v>
-      </c>
-      <c r="C11">
-        <v>1.9330000000000001</v>
-      </c>
-      <c r="D11">
-        <v>1.9330000000000001</v>
-      </c>
-      <c r="E11">
-        <f t="shared" si="0"/>
-        <v>62</v>
+        <v>1.895</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12">
+        <v>1.972</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13">
+        <v>1.788</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>10</v>
       </c>
-      <c r="B12">
-        <v>1.944</v>
-      </c>
-      <c r="C12">
-        <v>1.944</v>
-      </c>
-      <c r="D12">
-        <v>1.944</v>
-      </c>
-      <c r="E12">
-        <f t="shared" si="0"/>
-        <v>67</v>
+      <c r="B14">
+        <v>2.0019999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
-        <v>1.9019999999999999</v>
-      </c>
-      <c r="C13">
-        <v>1.9019999999999999</v>
-      </c>
-      <c r="D13">
-        <v>1.9019999999999999</v>
-      </c>
-      <c r="E13">
-        <f t="shared" si="0"/>
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14">
-        <v>1.9359999999999999</v>
-      </c>
-      <c r="C14">
-        <v>1.9359999999999999</v>
-      </c>
-      <c r="D14">
-        <v>1.9359999999999999</v>
-      </c>
-      <c r="E14">
-        <f t="shared" si="0"/>
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15">
-        <v>1.958</v>
-      </c>
-      <c r="C15">
-        <v>1.958</v>
-      </c>
-      <c r="D15">
-        <v>1.958</v>
-      </c>
-      <c r="E15">
-        <f t="shared" si="0"/>
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16">
-        <v>1.9379999999999999</v>
-      </c>
-      <c r="C16">
-        <v>1.9379999999999999</v>
-      </c>
-      <c r="D16">
-        <v>1.9379999999999999</v>
-      </c>
-      <c r="E16">
-        <f t="shared" si="0"/>
-        <v>88.5</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18">
-        <f>CORREL(E2:E16,B2:B16)</f>
-        <v>-0.45099742166124357</v>
+        <v>1.978</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C16">
-    <sortCondition ref="A2:A16"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B15">
+    <sortCondition ref="A1:A15"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
